--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/117.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/117.xlsx
@@ -426,13 +426,13 @@
         <v>-19.93970551150563</v>
       </c>
       <c r="E2">
-        <v>-17.32897317916552</v>
+        <v>-18.45227021371617</v>
       </c>
       <c r="F2">
-        <v>-3.163991688977762</v>
+        <v>-2.680848886397159</v>
       </c>
       <c r="G2">
-        <v>-14.49779874352401</v>
+        <v>-14.0790478382616</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.38430527179252</v>
       </c>
       <c r="E3">
-        <v>-18.48021995529151</v>
+        <v>-19.70149505347211</v>
       </c>
       <c r="F3">
-        <v>-3.246363715144742</v>
+        <v>-2.919141195323479</v>
       </c>
       <c r="G3">
-        <v>-15.12829545202375</v>
+        <v>-13.26108652278232</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.76525149861663</v>
       </c>
       <c r="E4">
-        <v>-17.06660245210912</v>
+        <v>-19.21947522314766</v>
       </c>
       <c r="F4">
-        <v>-3.289384976209135</v>
+        <v>-2.683989227221172</v>
       </c>
       <c r="G4">
-        <v>-14.28956377383108</v>
+        <v>-13.01767866200741</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.00453118025656</v>
       </c>
       <c r="E5">
-        <v>-19.22576527354432</v>
+        <v>-19.62031309993661</v>
       </c>
       <c r="F5">
-        <v>-3.128436503314802</v>
+        <v>-2.553183387379907</v>
       </c>
       <c r="G5">
-        <v>-14.92468034863087</v>
+        <v>-13.35807557544635</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.07956377433496</v>
       </c>
       <c r="E6">
-        <v>-18.43981691019507</v>
+        <v>-20.43364061713623</v>
       </c>
       <c r="F6">
-        <v>-3.522393129472996</v>
+        <v>-2.301507974693959</v>
       </c>
       <c r="G6">
-        <v>-14.76233781647609</v>
+        <v>-13.28437621065109</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.97034947161926</v>
       </c>
       <c r="E7">
-        <v>-19.58014553548857</v>
+        <v>-21.10508198672752</v>
       </c>
       <c r="F7">
-        <v>-3.175397479746909</v>
+        <v>-2.247471083907139</v>
       </c>
       <c r="G7">
-        <v>-13.90606852328914</v>
+        <v>-12.3615914364891</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.67623758502488</v>
       </c>
       <c r="E8">
-        <v>-19.22994052657939</v>
+        <v>-21.40897882043426</v>
       </c>
       <c r="F8">
-        <v>-2.91791355483253</v>
+        <v>-2.357225622941059</v>
       </c>
       <c r="G8">
-        <v>-14.54333529741668</v>
+        <v>-12.3029020851689</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.18642719920453</v>
       </c>
       <c r="E9">
-        <v>-19.93178607065818</v>
+        <v>-21.46263670895114</v>
       </c>
       <c r="F9">
-        <v>-3.230985902679172</v>
+        <v>-2.425741547561412</v>
       </c>
       <c r="G9">
-        <v>-14.14673028653923</v>
+        <v>-12.19478959949292</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.51146757670275</v>
       </c>
       <c r="E10">
-        <v>-20.01406391490355</v>
+        <v>-21.70925287493487</v>
       </c>
       <c r="F10">
-        <v>-3.050158268852457</v>
+        <v>-2.442715624012177</v>
       </c>
       <c r="G10">
-        <v>-13.0993895470077</v>
+        <v>-11.22283329243614</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.67218087572685</v>
       </c>
       <c r="E11">
-        <v>-21.48688215878821</v>
+        <v>-22.6286236679721</v>
       </c>
       <c r="F11">
-        <v>-2.870075337320858</v>
+        <v>-2.310038502207988</v>
       </c>
       <c r="G11">
-        <v>-13.33240891588038</v>
+        <v>-11.05053926039031</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.69585430484311</v>
       </c>
       <c r="E12">
-        <v>-22.22206180003747</v>
+        <v>-23.20865778971857</v>
       </c>
       <c r="F12">
-        <v>-1.857464113525492</v>
+        <v>-2.623560653554351</v>
       </c>
       <c r="G12">
-        <v>-12.23437048196045</v>
+        <v>-10.97825018799479</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.60578647927407</v>
       </c>
       <c r="E13">
-        <v>-21.19940557183329</v>
+        <v>-23.74359283882264</v>
       </c>
       <c r="F13">
-        <v>-2.43556764169342</v>
+        <v>-2.2816950831538</v>
       </c>
       <c r="G13">
-        <v>-12.15883045384536</v>
+        <v>-10.56065466312558</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.45501822916269</v>
       </c>
       <c r="E14">
-        <v>-22.7237306790812</v>
+        <v>-24.08320121855387</v>
       </c>
       <c r="F14">
-        <v>-2.539600647076204</v>
+        <v>-2.363372109069832</v>
       </c>
       <c r="G14">
-        <v>-12.54266503530508</v>
+        <v>-10.33712662831399</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.29481107322649</v>
       </c>
       <c r="E15">
-        <v>-24.36141254768911</v>
+        <v>-24.84632154443045</v>
       </c>
       <c r="F15">
-        <v>-2.764963797579629</v>
+        <v>-2.114659766583697</v>
       </c>
       <c r="G15">
-        <v>-11.70841086995428</v>
+        <v>-9.813060648356279</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.16824699990753</v>
       </c>
       <c r="E16">
-        <v>-24.15753611938978</v>
+        <v>-25.31206603917133</v>
       </c>
       <c r="F16">
-        <v>-2.313277418752934</v>
+        <v>-2.126855819855114</v>
       </c>
       <c r="G16">
-        <v>-12.23132478006432</v>
+        <v>-9.36922242899727</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.12463780151024</v>
       </c>
       <c r="E17">
-        <v>-23.97191396981538</v>
+        <v>-26.41945001605903</v>
       </c>
       <c r="F17">
-        <v>-2.789110707371235</v>
+        <v>-1.983306375889182</v>
       </c>
       <c r="G17">
-        <v>-10.29391407738988</v>
+        <v>-9.181170200184509</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.20786004876586</v>
       </c>
       <c r="E18">
-        <v>-24.7952222437279</v>
+        <v>-26.76025844140229</v>
       </c>
       <c r="F18">
-        <v>-2.273008822568045</v>
+        <v>-2.275363871094204</v>
       </c>
       <c r="G18">
-        <v>-9.520517670687502</v>
+        <v>-8.461719133044555</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.44342761636649</v>
       </c>
       <c r="E19">
-        <v>-25.25486235550644</v>
+        <v>-27.25633465504655</v>
       </c>
       <c r="F19">
-        <v>-2.631076430999951</v>
+        <v>-2.207005336280383</v>
       </c>
       <c r="G19">
-        <v>-9.619910179413042</v>
+        <v>-8.303253249716262</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.834331468074382</v>
       </c>
       <c r="E20">
-        <v>-26.46607971291601</v>
+        <v>-27.89708655628786</v>
       </c>
       <c r="F20">
-        <v>-2.103947319330694</v>
+        <v>-1.606506067010368</v>
       </c>
       <c r="G20">
-        <v>-9.589794146642291</v>
+        <v>-7.552875066148437</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.390025588463651</v>
       </c>
       <c r="E21">
-        <v>-26.68055729886729</v>
+        <v>-28.59948457419558</v>
       </c>
       <c r="F21">
-        <v>-1.973390818077672</v>
+        <v>-1.624303540659515</v>
       </c>
       <c r="G21">
-        <v>-9.805688063440323</v>
+        <v>-8.075342052610676</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.103065299245952</v>
       </c>
       <c r="E22">
-        <v>-27.33012613900154</v>
+        <v>-29.62240571812922</v>
       </c>
       <c r="F22">
-        <v>-2.176528042796583</v>
+        <v>-1.245362730411868</v>
       </c>
       <c r="G22">
-        <v>-7.911685233876805</v>
+        <v>-7.791992459904455</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.949644498179099</v>
       </c>
       <c r="E23">
-        <v>-26.87876860618302</v>
+        <v>-29.00971450607643</v>
       </c>
       <c r="F23">
-        <v>-2.180498407758201</v>
+        <v>-1.262005459901512</v>
       </c>
       <c r="G23">
-        <v>-9.084810151172944</v>
+        <v>-7.639823234191856</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.909043969546255</v>
       </c>
       <c r="E24">
-        <v>-28.84446143258853</v>
+        <v>-29.20886773598576</v>
       </c>
       <c r="F24">
-        <v>-1.406786686195407</v>
+        <v>-0.9897484307256075</v>
       </c>
       <c r="G24">
-        <v>-9.226872281354149</v>
+        <v>-7.589072571074828</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.960101705524307</v>
       </c>
       <c r="E25">
-        <v>-29.12561174135474</v>
+        <v>-30.0545013867561</v>
       </c>
       <c r="F25">
-        <v>-2.091713989526151</v>
+        <v>-1.349275622521246</v>
       </c>
       <c r="G25">
-        <v>-8.173608975852863</v>
+        <v>-7.73460415298119</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.076846618014711</v>
       </c>
       <c r="E26">
-        <v>-29.42016633318366</v>
+        <v>-30.85271965042913</v>
       </c>
       <c r="F26">
-        <v>-1.547021003815336</v>
+        <v>-0.7410725364051959</v>
       </c>
       <c r="G26">
-        <v>-8.513363643457186</v>
+        <v>-7.810283224008929</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.228850894971474</v>
       </c>
       <c r="E27">
-        <v>-28.54617537817729</v>
+        <v>-30.68877077745543</v>
       </c>
       <c r="F27">
-        <v>-2.002169958385732</v>
+        <v>-1.033494513267449</v>
       </c>
       <c r="G27">
-        <v>-9.731915866643204</v>
+        <v>-8.715104978074834</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.397307613767612</v>
       </c>
       <c r="E28">
-        <v>-30.98814592986551</v>
+        <v>-31.27732069457332</v>
       </c>
       <c r="F28">
-        <v>-1.850415535295071</v>
+        <v>-1.116935133384041</v>
       </c>
       <c r="G28">
-        <v>-8.915422778110594</v>
+        <v>-8.004109044242178</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.568689736987475</v>
       </c>
       <c r="E29">
-        <v>-27.32595541444047</v>
+        <v>-30.41854541223272</v>
       </c>
       <c r="F29">
-        <v>-2.23049866419118</v>
+        <v>-1.114890722633932</v>
       </c>
       <c r="G29">
-        <v>-8.024531799673943</v>
+        <v>-8.145499133678911</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.728234459274704</v>
       </c>
       <c r="E30">
-        <v>-28.45730860425077</v>
+        <v>-31.44902910775916</v>
       </c>
       <c r="F30">
-        <v>-1.500628287421549</v>
+        <v>-1.122503419065659</v>
       </c>
       <c r="G30">
-        <v>-9.434205127387624</v>
+        <v>-8.162048550829729</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.868501544983689</v>
       </c>
       <c r="E31">
-        <v>-28.86403802572369</v>
+        <v>-29.90039741627508</v>
       </c>
       <c r="F31">
-        <v>-1.183394221743242</v>
+        <v>-1.066637493053457</v>
       </c>
       <c r="G31">
-        <v>-10.64233244267048</v>
+        <v>-7.680701850510776</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.990660524195043</v>
       </c>
       <c r="E32">
-        <v>-29.96224957850884</v>
+        <v>-29.66972600727237</v>
       </c>
       <c r="F32">
-        <v>-1.73668980293213</v>
+        <v>-0.8119153450600124</v>
       </c>
       <c r="G32">
-        <v>-8.437432970968462</v>
+        <v>-8.300363143460478</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.09912504785277</v>
       </c>
       <c r="E33">
-        <v>-27.83035043483682</v>
+        <v>-29.68296726527079</v>
       </c>
       <c r="F33">
-        <v>-1.829384943672798</v>
+        <v>-0.9308258289970758</v>
       </c>
       <c r="G33">
-        <v>-7.972864115442537</v>
+        <v>-8.761174529799332</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.19552236807384</v>
       </c>
       <c r="E34">
-        <v>-29.66564358795445</v>
+        <v>-30.19681773939516</v>
       </c>
       <c r="F34">
-        <v>-1.924258690682828</v>
+        <v>-0.7256541339368887</v>
       </c>
       <c r="G34">
-        <v>-8.667863493229433</v>
+        <v>-7.892156325740645</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.28517906136601</v>
       </c>
       <c r="E35">
-        <v>-28.77835476902456</v>
+        <v>-29.41658431024359</v>
       </c>
       <c r="F35">
-        <v>-1.376798957846662</v>
+        <v>-0.9748320189033968</v>
       </c>
       <c r="G35">
-        <v>-9.859060678624452</v>
+        <v>-8.814904683901702</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.37755536107499</v>
       </c>
       <c r="E36">
-        <v>-29.0852630379464</v>
+        <v>-29.00289009574687</v>
       </c>
       <c r="F36">
-        <v>-1.056843705250159</v>
+        <v>-0.9102226749546465</v>
       </c>
       <c r="G36">
-        <v>-9.563250192508415</v>
+        <v>-8.515704199153451</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.47323147508222</v>
       </c>
       <c r="E37">
-        <v>-27.5171430585703</v>
+        <v>-29.516011485556</v>
       </c>
       <c r="F37">
-        <v>-1.035339287473484</v>
+        <v>-0.7909352838493093</v>
       </c>
       <c r="G37">
-        <v>-9.497019418449757</v>
+        <v>-8.585387872209571</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.57101188142582</v>
       </c>
       <c r="E38">
-        <v>-28.48107856431703</v>
+        <v>-28.00803869794979</v>
       </c>
       <c r="F38">
-        <v>-1.098892462983665</v>
+        <v>-0.9529805151849486</v>
       </c>
       <c r="G38">
-        <v>-8.440256866313462</v>
+        <v>-8.43059007333879</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.67253074266595</v>
       </c>
       <c r="E39">
-        <v>-28.12268607440198</v>
+        <v>-28.48890376740228</v>
       </c>
       <c r="F39">
-        <v>-1.416262380916031</v>
+        <v>-0.723508662363638</v>
       </c>
       <c r="G39">
-        <v>-8.896453352170569</v>
+        <v>-8.308093267294677</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.77652502623921</v>
       </c>
       <c r="E40">
-        <v>-27.19626897580881</v>
+        <v>-27.65860352962191</v>
       </c>
       <c r="F40">
-        <v>-0.7087678644308207</v>
+        <v>-0.8273262922216944</v>
       </c>
       <c r="G40">
-        <v>-9.146707421120697</v>
+        <v>-8.348998367977911</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.87572629091145</v>
       </c>
       <c r="E41">
-        <v>-25.27630015145875</v>
+        <v>-26.99630967752612</v>
       </c>
       <c r="F41">
-        <v>-1.584193162648561</v>
+        <v>-0.6784189678944552</v>
       </c>
       <c r="G41">
-        <v>-9.237164767435743</v>
+        <v>-8.775959426177716</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.9665010080497</v>
       </c>
       <c r="E42">
-        <v>-26.64129542922079</v>
+        <v>-27.04259068188451</v>
       </c>
       <c r="F42">
-        <v>-1.249381140682848</v>
+        <v>-0.4647266857290724</v>
       </c>
       <c r="G42">
-        <v>-9.069810069334505</v>
+        <v>-8.750713205895234</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.04936590466188</v>
       </c>
       <c r="E43">
-        <v>-24.5704016231431</v>
+        <v>-26.60861343230743</v>
       </c>
       <c r="F43">
-        <v>-0.8408063149674507</v>
+        <v>-0.7743654506911108</v>
       </c>
       <c r="G43">
-        <v>-9.697996017047831</v>
+        <v>-8.924877696170752</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.11764850364681</v>
       </c>
       <c r="E44">
-        <v>-26.9038472952375</v>
+        <v>-25.80994458547064</v>
       </c>
       <c r="F44">
-        <v>-0.9933973891349392</v>
+        <v>-0.6807383966222939</v>
       </c>
       <c r="G44">
-        <v>-9.348756636473496</v>
+        <v>-8.954083328918202</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.16709410261548</v>
       </c>
       <c r="E45">
-        <v>-25.27667601480139</v>
+        <v>-25.53239894201453</v>
       </c>
       <c r="F45">
-        <v>-1.344232521773003</v>
+        <v>-0.6420958856490997</v>
       </c>
       <c r="G45">
-        <v>-10.10232618594118</v>
+        <v>-8.832318153438269</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.19840820879458</v>
       </c>
       <c r="E46">
-        <v>-23.54216178648746</v>
+        <v>-25.58541378722233</v>
       </c>
       <c r="F46">
-        <v>-1.483978930992682</v>
+        <v>-0.7484126999614023</v>
       </c>
       <c r="G46">
-        <v>-9.537116746021409</v>
+        <v>-8.8627023403977</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.20998462163098</v>
       </c>
       <c r="E47">
-        <v>-22.37589859055203</v>
+        <v>-24.2706619285754</v>
       </c>
       <c r="F47">
-        <v>-0.6907276791326531</v>
+        <v>-0.4246800920081331</v>
       </c>
       <c r="G47">
-        <v>-10.55085544832933</v>
+        <v>-8.73938120851431</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.19639969564767</v>
       </c>
       <c r="E48">
-        <v>-22.91067061459184</v>
+        <v>-24.43901700675856</v>
       </c>
       <c r="F48">
-        <v>-0.9168545843814594</v>
+        <v>-0.5349606443428313</v>
       </c>
       <c r="G48">
-        <v>-9.342430183947949</v>
+        <v>-9.120607080089082</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.15775751891492</v>
       </c>
       <c r="E49">
-        <v>-23.85329965013247</v>
+        <v>-24.03198417752712</v>
       </c>
       <c r="F49">
-        <v>-1.431508482964556</v>
+        <v>-0.3666678660552781</v>
       </c>
       <c r="G49">
-        <v>-9.496039496970132</v>
+        <v>-8.698343686009503</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.09662661245803</v>
       </c>
       <c r="E50">
-        <v>-21.93004315365284</v>
+        <v>-23.60419282344453</v>
       </c>
       <c r="F50">
-        <v>-1.390464534890646</v>
+        <v>-0.5334422468934998</v>
       </c>
       <c r="G50">
-        <v>-11.11529353113846</v>
+        <v>-9.157489867942102</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.00871184262514</v>
       </c>
       <c r="E51">
-        <v>-23.33520146738891</v>
+        <v>-22.73503827867835</v>
       </c>
       <c r="F51">
-        <v>-0.6657010431592745</v>
+        <v>-0.6332058466822554</v>
       </c>
       <c r="G51">
-        <v>-11.4343374258491</v>
+        <v>-9.690716127406974</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.8941820274821</v>
       </c>
       <c r="E52">
-        <v>-22.12560077520008</v>
+        <v>-22.15221008846915</v>
       </c>
       <c r="F52">
-        <v>-1.215165425110214</v>
+        <v>-0.5433718869508575</v>
       </c>
       <c r="G52">
-        <v>-10.38833083616989</v>
+        <v>-9.505004454290479</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.75671741077874</v>
       </c>
       <c r="E53">
-        <v>-21.19126337556749</v>
+        <v>-21.04982554688592</v>
       </c>
       <c r="F53">
-        <v>-0.6520164136650266</v>
+        <v>-0.6690940360411413</v>
       </c>
       <c r="G53">
-        <v>-10.54605846784293</v>
+        <v>-9.22381995836694</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.5965286547236</v>
       </c>
       <c r="E54">
-        <v>-21.15797909161111</v>
+        <v>-20.86592421743443</v>
       </c>
       <c r="F54">
-        <v>-1.063537742232182</v>
+        <v>-0.5783579842080946</v>
       </c>
       <c r="G54">
-        <v>-11.30148523335814</v>
+        <v>-9.462215653195399</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.41157210904251</v>
       </c>
       <c r="E55">
-        <v>-20.10452471168077</v>
+        <v>-20.59619472011556</v>
       </c>
       <c r="F55">
-        <v>-1.155095534528806</v>
+        <v>-0.7752004450331327</v>
       </c>
       <c r="G55">
-        <v>-10.11050654396872</v>
+        <v>-9.407740626346691</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.20622460771472</v>
       </c>
       <c r="E56">
-        <v>-19.38924771369523</v>
+        <v>-21.03756243927315</v>
       </c>
       <c r="F56">
-        <v>-0.6834073963941139</v>
+        <v>-0.7396444310027696</v>
       </c>
       <c r="G56">
-        <v>-11.34787590799995</v>
+        <v>-9.819314268879962</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.985249625686814</v>
       </c>
       <c r="E57">
-        <v>-21.16893799870968</v>
+        <v>-21.21619262497972</v>
       </c>
       <c r="F57">
-        <v>-1.332060491156267</v>
+        <v>-0.7861166706672246</v>
       </c>
       <c r="G57">
-        <v>-11.15549017507628</v>
+        <v>-9.517193882966074</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.747292728825647</v>
       </c>
       <c r="E58">
-        <v>-19.41321692661782</v>
+        <v>-20.53553128230881</v>
       </c>
       <c r="F58">
-        <v>-1.378415931016927</v>
+        <v>-0.7251513149233894</v>
       </c>
       <c r="G58">
-        <v>-12.03837956494452</v>
+        <v>-9.393458932890274</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.497846704328696</v>
       </c>
       <c r="E59">
-        <v>-19.78023615951749</v>
+        <v>-20.29728373629126</v>
       </c>
       <c r="F59">
-        <v>-1.322519355410822</v>
+        <v>-0.7201222964209936</v>
       </c>
       <c r="G59">
-        <v>-11.17245672096505</v>
+        <v>-9.954821518893411</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.244904926955755</v>
       </c>
       <c r="E60">
-        <v>-18.81323487686757</v>
+        <v>-20.10707877102109</v>
       </c>
       <c r="F60">
-        <v>-1.872806306192742</v>
+        <v>-0.8842566703464932</v>
       </c>
       <c r="G60">
-        <v>-10.79734542700131</v>
+        <v>-10.46242084533878</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.992371497944283</v>
       </c>
       <c r="E61">
-        <v>-18.67594965885104</v>
+        <v>-19.96075924735926</v>
       </c>
       <c r="F61">
-        <v>-1.659903458162227</v>
+        <v>-0.3664326097128831</v>
       </c>
       <c r="G61">
-        <v>-10.20012963280787</v>
+        <v>-10.10151510228406</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.742466905988795</v>
       </c>
       <c r="E62">
-        <v>-19.43277540585695</v>
+        <v>-19.34639023568663</v>
       </c>
       <c r="F62">
-        <v>-0.6765982163431019</v>
+        <v>-0.5649889626943133</v>
       </c>
       <c r="G62">
-        <v>-11.50737799208204</v>
+        <v>-10.67134606377665</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.502119525439062</v>
       </c>
       <c r="E63">
-        <v>-19.30752687175281</v>
+        <v>-19.7262839201901</v>
       </c>
       <c r="F63">
-        <v>-1.053385271343471</v>
+        <v>-0.7660768064586989</v>
       </c>
       <c r="G63">
-        <v>-10.64140217937394</v>
+        <v>-10.25586597750704</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.276080460776869</v>
       </c>
       <c r="E64">
-        <v>-17.91011224856986</v>
+        <v>-19.45958397198236</v>
       </c>
       <c r="F64">
-        <v>-1.189792531562466</v>
+        <v>-0.888988304951284</v>
       </c>
       <c r="G64">
-        <v>-10.95406996337595</v>
+        <v>-9.862993606725107</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.062105963132497</v>
       </c>
       <c r="E65">
-        <v>-17.45519986365532</v>
+        <v>-18.70939696787169</v>
       </c>
       <c r="F65">
-        <v>-1.324104022252377</v>
+        <v>-0.7666400962926027</v>
       </c>
       <c r="G65">
-        <v>-11.16127700867893</v>
+        <v>-10.62984837544188</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.863299304770978</v>
       </c>
       <c r="E66">
-        <v>-18.77771352675141</v>
+        <v>-19.29820727224502</v>
       </c>
       <c r="F66">
-        <v>-1.367882411122929</v>
+        <v>-0.7310120142981958</v>
       </c>
       <c r="G66">
-        <v>-11.52482125652846</v>
+        <v>-10.35719515537305</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.683760331895783</v>
       </c>
       <c r="E67">
-        <v>-16.09145897319341</v>
+        <v>-18.24814471934642</v>
       </c>
       <c r="F67">
-        <v>-1.475687801658062</v>
+        <v>-1.040375761282505</v>
       </c>
       <c r="G67">
-        <v>-11.00087114566463</v>
+        <v>-10.43782680252754</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.523304017716129</v>
       </c>
       <c r="E68">
-        <v>-19.20295534996768</v>
+        <v>-18.93632332887006</v>
       </c>
       <c r="F68">
-        <v>-1.658144005798681</v>
+        <v>-0.9658723970747173</v>
       </c>
       <c r="G68">
-        <v>-11.34240688676908</v>
+        <v>-10.18938029144185</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.38121843329905</v>
       </c>
       <c r="E69">
-        <v>-16.37674830720264</v>
+        <v>-18.25283621841837</v>
       </c>
       <c r="F69">
-        <v>-1.273077418607331</v>
+        <v>-0.7034306932545835</v>
       </c>
       <c r="G69">
-        <v>-11.60900842959212</v>
+        <v>-10.68039047418994</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.26083163166659</v>
       </c>
       <c r="E70">
-        <v>-17.58738149146522</v>
+        <v>-18.68233480720185</v>
       </c>
       <c r="F70">
-        <v>-1.630674514354447</v>
+        <v>-1.085178840630319</v>
       </c>
       <c r="G70">
-        <v>-10.91309203069085</v>
+        <v>-10.75703953506068</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.16507805626983</v>
       </c>
       <c r="E71">
-        <v>-18.04241614517796</v>
+        <v>-18.29817982865717</v>
       </c>
       <c r="F71">
-        <v>-2.006298541521285</v>
+        <v>-0.9657307462488386</v>
       </c>
       <c r="G71">
-        <v>-10.28575689318112</v>
+        <v>-9.979365903521568</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.091114777061343</v>
       </c>
       <c r="E72">
-        <v>-18.65508245062369</v>
+        <v>-18.53300384832492</v>
       </c>
       <c r="F72">
-        <v>-1.260536764496349</v>
+        <v>-1.241921692220639</v>
       </c>
       <c r="G72">
-        <v>-9.908930736628035</v>
+        <v>-10.14388677464119</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.039455486520018</v>
       </c>
       <c r="E73">
-        <v>-17.69538106807414</v>
+        <v>-18.54427522013001</v>
       </c>
       <c r="F73">
-        <v>-1.357806150035275</v>
+        <v>-1.191464176981315</v>
       </c>
       <c r="G73">
-        <v>-11.3324785606968</v>
+        <v>-10.09032876890686</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.012724936874853</v>
       </c>
       <c r="E74">
-        <v>-17.25700667023562</v>
+        <v>-19.05148695135913</v>
       </c>
       <c r="F74">
-        <v>-1.42535205642695</v>
+        <v>-1.488066924125498</v>
       </c>
       <c r="G74">
-        <v>-10.12992289355654</v>
+        <v>-10.2950793894197</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.008948052915031</v>
       </c>
       <c r="E75">
-        <v>-18.53064904184093</v>
+        <v>-19.61344340486697</v>
       </c>
       <c r="F75">
-        <v>-1.790710954738297</v>
+        <v>-1.075191214854765</v>
       </c>
       <c r="G75">
-        <v>-10.06735027231878</v>
+        <v>-9.938692541026082</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.024786384116608</v>
       </c>
       <c r="E76">
-        <v>-17.43939096089455</v>
+        <v>-19.47433321182535</v>
       </c>
       <c r="F76">
-        <v>-2.168957593102399</v>
+        <v>-1.368925325683053</v>
       </c>
       <c r="G76">
-        <v>-10.97339692823421</v>
+        <v>-9.705941326342082</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.059223504991981</v>
       </c>
       <c r="E77">
-        <v>-21.40564133509061</v>
+        <v>-19.07758907553934</v>
       </c>
       <c r="F77">
-        <v>-2.35567243406081</v>
+        <v>-1.314062552595642</v>
       </c>
       <c r="G77">
-        <v>-10.49397696541912</v>
+        <v>-9.941036407267886</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.11238967972609</v>
       </c>
       <c r="E78">
-        <v>-18.35343626849876</v>
+        <v>-20.12778295418416</v>
       </c>
       <c r="F78">
-        <v>-2.326090605739437</v>
+        <v>-1.505933152269077</v>
       </c>
       <c r="G78">
-        <v>-10.20082153682557</v>
+        <v>-9.32420563075426</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.179170316274195</v>
       </c>
       <c r="E79">
-        <v>-20.15942793054976</v>
+        <v>-20.95920172504443</v>
       </c>
       <c r="F79">
-        <v>-1.89147687908444</v>
+        <v>-1.738931365124106</v>
       </c>
       <c r="G79">
-        <v>-10.49768146587756</v>
+        <v>-9.47138255379364</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.255788630143146</v>
       </c>
       <c r="E80">
-        <v>-18.84883321104187</v>
+        <v>-21.21385593239176</v>
       </c>
       <c r="F80">
-        <v>-1.900642764396417</v>
+        <v>-1.6410763238314</v>
       </c>
       <c r="G80">
-        <v>-10.67161421796533</v>
+        <v>-9.613269225061263</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.34318460143675</v>
       </c>
       <c r="E81">
-        <v>-20.30168088455271</v>
+        <v>-21.17900479642873</v>
       </c>
       <c r="F81">
-        <v>-2.636643059946763</v>
+        <v>-1.751551542505756</v>
       </c>
       <c r="G81">
-        <v>-9.46601947002002</v>
+        <v>-9.667611830088401</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.438506618324716</v>
       </c>
       <c r="E82">
-        <v>-19.88667794106778</v>
+        <v>-21.23288458017199</v>
       </c>
       <c r="F82">
-        <v>-2.356488375952568</v>
+        <v>-1.754580053730391</v>
       </c>
       <c r="G82">
-        <v>-10.46610217197845</v>
+        <v>-9.522954232204405</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.538532016378408</v>
       </c>
       <c r="E83">
-        <v>-21.47800182125917</v>
+        <v>-23.0623790223228</v>
       </c>
       <c r="F83">
-        <v>-2.734686969007307</v>
+        <v>-2.094894920352901</v>
       </c>
       <c r="G83">
-        <v>-10.28583634627406</v>
+        <v>-9.111324310396967</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.642852163975272</v>
       </c>
       <c r="E84">
-        <v>-22.06292669493392</v>
+        <v>-23.6311553576862</v>
       </c>
       <c r="F84">
-        <v>-3.085835224523629</v>
+        <v>-2.203030829481751</v>
       </c>
       <c r="G84">
-        <v>-10.50951335563492</v>
+        <v>-9.263089649553775</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.753961405155594</v>
       </c>
       <c r="E85">
-        <v>-21.93053222884567</v>
+        <v>-23.9079900307231</v>
       </c>
       <c r="F85">
-        <v>-2.609370719944395</v>
+        <v>-2.062145415083222</v>
       </c>
       <c r="G85">
-        <v>-9.078731989562842</v>
+        <v>-8.74014594453388</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.869692705954647</v>
       </c>
       <c r="E86">
-        <v>-22.69622925643261</v>
+        <v>-24.62204886920058</v>
       </c>
       <c r="F86">
-        <v>-2.779946478794064</v>
+        <v>-1.962996463907344</v>
       </c>
       <c r="G86">
-        <v>-9.360598457867468</v>
+        <v>-8.621697935684297</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.988337190145601</v>
       </c>
       <c r="E87">
-        <v>-26.64107806246842</v>
+        <v>-26.2751411348566</v>
       </c>
       <c r="F87">
-        <v>-3.048137052389626</v>
+        <v>-2.302970871527303</v>
       </c>
       <c r="G87">
-        <v>-9.068932774766598</v>
+        <v>-9.190217921143338</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.115057097412887</v>
       </c>
       <c r="E88">
-        <v>-26.50150596507801</v>
+        <v>-26.60594616111691</v>
       </c>
       <c r="F88">
-        <v>-3.318414283472841</v>
+        <v>-2.146081398906688</v>
       </c>
       <c r="G88">
-        <v>-10.6247997934945</v>
+        <v>-9.12193460885033</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.249469520567366</v>
       </c>
       <c r="E89">
-        <v>-27.29712714890764</v>
+        <v>-28.00055765888912</v>
       </c>
       <c r="F89">
-        <v>-3.193555293216274</v>
+        <v>-2.464895989589536</v>
       </c>
       <c r="G89">
-        <v>-9.13787819616746</v>
+        <v>-9.442743024333405</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.389657712228679</v>
       </c>
       <c r="E90">
-        <v>-27.26924533444242</v>
+        <v>-29.33811491263868</v>
       </c>
       <c r="F90">
-        <v>-2.860378468503687</v>
+        <v>-2.758069295686129</v>
       </c>
       <c r="G90">
-        <v>-10.1225602402772</v>
+        <v>-9.422618218000174</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.535843147700632</v>
       </c>
       <c r="E91">
-        <v>-28.32435713585957</v>
+        <v>-30.46210933218651</v>
       </c>
       <c r="F91">
-        <v>-3.123353640931224</v>
+        <v>-2.647547688437216</v>
       </c>
       <c r="G91">
-        <v>-10.42550826257591</v>
+        <v>-9.540764967205686</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.690495529920176</v>
       </c>
       <c r="E92">
-        <v>-31.58102280389773</v>
+        <v>-31.80804879132427</v>
       </c>
       <c r="F92">
-        <v>-3.708885139600055</v>
+        <v>-2.487971820329322</v>
       </c>
       <c r="G92">
-        <v>-11.03399315378503</v>
+        <v>-9.560191248430129</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.849839069848031</v>
       </c>
       <c r="E93">
-        <v>-32.80805812101609</v>
+        <v>-33.71651529169484</v>
       </c>
       <c r="F93">
-        <v>-3.558149608414837</v>
+        <v>-2.856697203765647</v>
       </c>
       <c r="G93">
-        <v>-10.21219988184405</v>
+        <v>-9.537494148212886</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.009493442552174</v>
       </c>
       <c r="E94">
-        <v>-34.83330943757048</v>
+        <v>-35.690862031929</v>
       </c>
       <c r="F94">
-        <v>-3.260657194680048</v>
+        <v>-2.789389038818575</v>
       </c>
       <c r="G94">
-        <v>-11.64341161883623</v>
+        <v>-9.264605879410761</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.171564828242838</v>
       </c>
       <c r="E95">
-        <v>-35.14419823514506</v>
+        <v>-37.01479310738949</v>
       </c>
       <c r="F95">
-        <v>-3.365848257691946</v>
+        <v>-3.168406887234684</v>
       </c>
       <c r="G95">
-        <v>-11.13863287719032</v>
+        <v>-9.92502991958551</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.330419226597845</v>
       </c>
       <c r="E96">
-        <v>-37.57982213051154</v>
+        <v>-39.3566300418201</v>
       </c>
       <c r="F96">
-        <v>-3.841500133849033</v>
+        <v>-3.285455201250254</v>
       </c>
       <c r="G96">
-        <v>-11.25442582851741</v>
+        <v>-9.351759301277614</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.478266667554474</v>
       </c>
       <c r="E97">
-        <v>-39.18905838964027</v>
+        <v>-40.70862859918012</v>
       </c>
       <c r="F97">
-        <v>-4.024551105784862</v>
+        <v>-3.379068173073223</v>
       </c>
       <c r="G97">
-        <v>-10.88055929967643</v>
+        <v>-9.910334407936684</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.608921739874251</v>
       </c>
       <c r="E98">
-        <v>-40.68436503544703</v>
+        <v>-42.31202765531297</v>
       </c>
       <c r="F98">
-        <v>-4.730913244030446</v>
+        <v>-3.24156663951513</v>
       </c>
       <c r="G98">
-        <v>-11.61204751039717</v>
+        <v>-10.39655754183498</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.715881155466398</v>
       </c>
       <c r="E99">
-        <v>-43.28341023656531</v>
+        <v>-44.59816209521225</v>
       </c>
       <c r="F99">
-        <v>-4.474270112029909</v>
+        <v>-3.559024364392193</v>
       </c>
       <c r="G99">
-        <v>-10.8571636743504</v>
+        <v>-11.12547676921725</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.786322176193487</v>
       </c>
       <c r="E100">
-        <v>-45.56538753732553</v>
+        <v>-46.58448212072268</v>
       </c>
       <c r="F100">
-        <v>-4.339851761945035</v>
+        <v>-3.424129703050711</v>
       </c>
       <c r="G100">
-        <v>-12.36846081848309</v>
+        <v>-10.71934566355054</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.8087484949156</v>
       </c>
       <c r="E101">
-        <v>-47.20567780696187</v>
+        <v>-48.51275616640281</v>
       </c>
       <c r="F101">
-        <v>-4.314930328631812</v>
+        <v>-3.600876799051235</v>
       </c>
       <c r="G101">
-        <v>-11.53839449323947</v>
+        <v>-10.83432753122051</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.780271964110135</v>
       </c>
       <c r="E102">
-        <v>-51.0005809137742</v>
+        <v>-49.82532982905205</v>
       </c>
       <c r="F102">
-        <v>-4.449873035282657</v>
+        <v>-4.067985722183251</v>
       </c>
       <c r="G102">
-        <v>-12.52554620432151</v>
+        <v>-11.39529285175893</v>
       </c>
     </row>
   </sheetData>
